--- a/data/trans_bre/P19-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P19-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 5,49</t>
+          <t>-1,38; 5,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,31; 10,1</t>
+          <t>3,44; 9,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 10,1</t>
+          <t>2,31; 10,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 3,39</t>
+          <t>-4,69; 3,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 30,05</t>
+          <t>-6,37; 31,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,35; 72,08</t>
+          <t>19,87; 69,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,41; 66,8</t>
+          <t>11,21; 65,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-23,16; 21,96</t>
+          <t>-22,86; 21,59</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,14; 14,64</t>
+          <t>8,08; 14,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,04; 10,38</t>
+          <t>4,29; 10,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,11; 9,91</t>
+          <t>4,09; 9,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 13,27</t>
+          <t>-2,33; 13,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,96; 60,05</t>
+          <t>30,19; 60,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,8; 42,69</t>
+          <t>15,62; 40,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,47; 33,84</t>
+          <t>12,42; 33,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 70,96</t>
+          <t>-7,41; 73,63</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 12,5</t>
+          <t>0,15; 12,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 11,85</t>
+          <t>-1,59; 11,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 9,33</t>
+          <t>-3,05; 9,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 15,72</t>
+          <t>4,81; 15,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 44,57</t>
+          <t>1,34; 44,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 37,36</t>
+          <t>-3,89; 35,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 26,74</t>
+          <t>-7,37; 27,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,59; 48,51</t>
+          <t>12,38; 47,29</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,39; 8,56</t>
+          <t>4,29; 8,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,4; 7,84</t>
+          <t>3,41; 7,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,01; 7,47</t>
+          <t>2,95; 7,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 10,26</t>
+          <t>0,0; 10,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,09; 35,84</t>
+          <t>16,31; 36,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,5; 32,98</t>
+          <t>13,22; 32,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,84; 26,6</t>
+          <t>9,63; 27,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 48,01</t>
+          <t>0,75; 50,94</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P19-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,65</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-3,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 5,77</t>
+          <t>-1,47; 5,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,44; 9,93</t>
+          <t>3,34; 10,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 10,18</t>
+          <t>2,42; 10,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 3,2</t>
+          <t>-3,62; 3,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 31,09</t>
+          <t>-6,83; 28,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,87; 69,33</t>
+          <t>18,55; 68,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,21; 65,38</t>
+          <t>12,13; 67,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-22,86; 21,59</t>
+          <t>-18,4; 26,27</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,69</t>
+          <t>6,05</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,49%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,08; 14,54</t>
+          <t>8,02; 14,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,29; 10,08</t>
+          <t>3,96; 10,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 9,97</t>
+          <t>4,09; 10,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 13,94</t>
+          <t>3,29; 8,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,19; 60,31</t>
+          <t>29,92; 61,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,62; 40,92</t>
+          <t>14,81; 41,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,42; 33,65</t>
+          <t>12,53; 34,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 73,63</t>
+          <t>12,2; 37,11</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,23</t>
+          <t>9,23</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>25,79%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 12,22</t>
+          <t>0,32; 12,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 11,74</t>
+          <t>-2,12; 11,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 9,65</t>
+          <t>-2,59; 9,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,81; 15,33</t>
+          <t>3,86; 14,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 44,78</t>
+          <t>1,17; 43,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 35,34</t>
+          <t>-5,76; 34,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 27,02</t>
+          <t>-6,16; 26,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,38; 47,29</t>
+          <t>10,12; 44,6</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,79</t>
+          <t>4,84</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,38%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,29; 8,66</t>
+          <t>4,14; 8,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,41; 7,68</t>
+          <t>3,34; 7,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,95; 7,65</t>
+          <t>2,91; 7,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,76</t>
+          <t>2,68; 7,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,31; 36,05</t>
+          <t>15,76; 35,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,22; 32,42</t>
+          <t>12,94; 33,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,63; 27,29</t>
+          <t>9,57; 25,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 50,94</t>
+          <t>9,87; 28,44</t>
         </is>
       </c>
     </row>
